--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-10).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>25</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 4.389,52</t>
+    <t>R$ 4.391,66</t>
   </si>
   <si>
-    <t>48.3</t>
+    <t>48.0</t>
   </si>
   <si>
-    <t>31.8</t>
+    <t>31.7</t>
   </si>
   <si>
-    <t>5.12</t>
+    <t>5.14</t>
   </si>
   <si>
     <t>19.2</t>
   </si>
   <si>
-    <t>7.5</t>
+    <t>7.4</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>42.6%</t>
+    <t>43.7%</t>
   </si>
   <si>
-    <t>20.3%</t>
+    <t>20.1%</t>
   </si>
   <si>
     <t>2.1%</t>
@@ -971,7 +971,7 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>5.0%</t>
+    <t>4.9%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -2206,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,14 +2236,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>8222.1800000000003</v>
+      </c>
+      <c r="N6" s="6">
+        <v>93</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>4.841392307692308</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.020720270270271</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.279054054054054</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.67567567567567566</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4958,7 +4970,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4988,14 +5000,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>4835.8299999999999</v>
+      </c>
+      <c r="N24" s="6">
+        <v>58</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.9628649122807018</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>18.52777857142857</v>
+      </c>
+      <c r="R24" s="8">
+        <v>7.46587380952381</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.23809523809523808</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6782,7 +6806,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6812,14 +6836,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>4154.3900000000003</v>
+      </c>
+      <c r="N36" s="6">
+        <v>31</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>8.2435483870967747</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>22.611111111111111</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.3712944444444446</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9071,7 +9107,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9101,8 +9137,12 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
       <c r="O51" s="6"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="8"/>
@@ -14773,7 +14813,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14801,14 +14841,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>2027.27</v>
+      </c>
+      <c r="N89" s="6">
+        <v>22</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>7.7272727272727275</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>21.716670000000001</v>
+      </c>
+      <c r="R89" s="8">
+        <v>3.7277777777777774</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -18015,7 +18067,9 @@
       <c r="N111" s="6">
         <v>4</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>3</v>
+      </c>
       <c r="P111" s="7">
         <v>10.591675</v>
       </c>
@@ -18025,31 +18079,75 @@
       <c r="R111" s="8">
         <v>3.1111</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -25114,7 +25212,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25144,14 +25242,26 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
+      <c r="M158" s="5">
+        <v>3122.5</v>
+      </c>
+      <c r="N158" s="6">
+        <v>31</v>
+      </c>
       <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
+      <c r="P158" s="7">
+        <v>5.4989258064516129</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>14.470833333333333</v>
+      </c>
+      <c r="R158" s="8">
+        <v>1.8868041666666666</v>
+      </c>
       <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
+      <c r="T158" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="U158" s="9"/>
       <c r="V158" s="9"/>
       <c r="W158" s="9"/>
@@ -28325,7 +28435,9 @@
       <c r="N179" s="6">
         <v>70</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>44</v>
+      </c>
       <c r="P179" s="7">
         <v>2.3518774647887324</v>
       </c>
@@ -28335,31 +28447,75 @@
       <c r="R179" s="8">
         <v>2.1106068181818181</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.84090909090909094</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
